--- a/data/trans_camb/P6904-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P6904-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-27,82; 1,45</t>
+          <t>-28,9; 2,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-32,76; -0,32</t>
+          <t>-32,92; 0,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 20,4</t>
+          <t>-15,09; 20,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 19,6</t>
+          <t>-25,38; 19,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 33,32</t>
+          <t>-22,47; 31,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 41,59</t>
+          <t>-4,06; 42,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 0,7</t>
+          <t>-26,02; -0,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 4,02</t>
+          <t>-26,04; 2,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 20,86</t>
+          <t>-7,43; 20,85</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 2,16</t>
+          <t>-38,38; 3,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,04; 0,15</t>
+          <t>-43,32; 0,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 30,01</t>
+          <t>-19,7; 30,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,34; 47,11</t>
+          <t>-39,62; 44,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,23; 74,38</t>
+          <t>-34,07; 75,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 104,18</t>
+          <t>-4,68; 113,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,54; 0,36</t>
+          <t>-35,52; -1,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,78; 6,43</t>
+          <t>-35,54; 4,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 32,72</t>
+          <t>-10,38; 32,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 15,61</t>
+          <t>-3,12; 14,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 22,74</t>
+          <t>4,18; 22,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 20,36</t>
+          <t>2,69; 21,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 11,51</t>
+          <t>-11,86; 14,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 27,11</t>
+          <t>4,54; 27,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 27,66</t>
+          <t>-0,55; 24,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 12,2</t>
+          <t>-2,73; 12,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,45; 21,7</t>
+          <t>7,34; 21,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 22,62</t>
+          <t>5,81; 22,35</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 34,25</t>
+          <t>-5,89; 32,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,38; 49,41</t>
+          <t>7,98; 49,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 44,14</t>
+          <t>5,15; 46,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 22,29</t>
+          <t>-18,87; 27,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,73; 53,01</t>
+          <t>7,96; 56,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 51,5</t>
+          <t>-1,43; 47,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 25,34</t>
+          <t>-5,01; 24,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,28; 44,83</t>
+          <t>12,77; 44,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,01; 45,07</t>
+          <t>10,4; 45,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 28,71</t>
+          <t>-7,61; 28,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 35,42</t>
+          <t>0,91; 35,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,94; 39,04</t>
+          <t>4,48; 38,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 15,03</t>
+          <t>-25,09; 13,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 36,55</t>
+          <t>2,12; 37,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 29,68</t>
+          <t>-1,22; 29,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 15,43</t>
+          <t>-10,38; 17,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 30,64</t>
+          <t>7,29; 32,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,27; 28,54</t>
+          <t>7,35; 29,7</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,99; 127,18</t>
+          <t>-21,35; 125,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 157,24</t>
+          <t>0,46; 154,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,32; 180,86</t>
+          <t>10,05; 168,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-51,08; 58,21</t>
+          <t>-59,99; 48,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,43; 134,55</t>
+          <t>2,91; 141,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 109,92</t>
+          <t>-3,16; 114,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,56; 58,13</t>
+          <t>-27,06; 60,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,75; 111,54</t>
+          <t>17,77; 123,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,39; 104,57</t>
+          <t>19,13; 114,29</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 10,01</t>
+          <t>-4,64; 9,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 14,33</t>
+          <t>-0,68; 14,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 16,48</t>
+          <t>1,18; 16,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 9,21</t>
+          <t>-10,06; 8,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 24,63</t>
+          <t>6,34; 24,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,72; 24,59</t>
+          <t>4,84; 25,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 7,28</t>
+          <t>-4,59; 6,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,2; 15,56</t>
+          <t>4,93; 16,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,9; 18,23</t>
+          <t>5,47; 17,97</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 19,87</t>
+          <t>-8,54; 19,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 29,29</t>
+          <t>-1,19; 29,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 33,43</t>
+          <t>2,08; 34,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 19,86</t>
+          <t>-17,56; 18,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,58; 54,02</t>
+          <t>10,71; 51,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,3; 51,86</t>
+          <t>8,2; 53,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 14,89</t>
+          <t>-8,27; 14,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,09; 32,05</t>
+          <t>8,89; 32,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,89; 37,16</t>
+          <t>9,95; 35,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6904-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P6904-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,98</t>
+          <t>7,51</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,77</t>
+          <t>12,61</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,37</t>
+          <t>7,08</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-28,9; 2,09</t>
+          <t>-28,74; 1,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-32,92; 0,56</t>
+          <t>-33,47; 0,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 20,98</t>
+          <t>-11,45; 22,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,38; 19,62</t>
+          <t>-24,55; 19,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 31,72</t>
+          <t>-20,37; 31,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 42,04</t>
+          <t>-9,84; 35,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,02; -0,65</t>
+          <t>-25,26; 0,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 2,72</t>
+          <t>-25,91; 2,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 20,85</t>
+          <t>-7,2; 18,94</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,38; 3,08</t>
+          <t>-38,05; 1,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,32; 0,98</t>
+          <t>-43,24; 0,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 30,1</t>
+          <t>-14,63; 33,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,62; 44,43</t>
+          <t>-39,13; 45,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,07; 75,2</t>
+          <t>-30,78; 74,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 113,98</t>
+          <t>-14,66; 82,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,52; -1,28</t>
+          <t>-35,24; 0,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,54; 4,11</t>
+          <t>-36,25; 4,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 32,67</t>
+          <t>-9,44; 29,48</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,09</t>
+          <t>14,37</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,18</t>
+          <t>5,81</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13,41</t>
+          <t>11,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 14,92</t>
+          <t>-3,12; 15,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 22,53</t>
+          <t>4,49; 22,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 21,03</t>
+          <t>5,71; 22,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 14,49</t>
+          <t>-13,86; 11,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 27,35</t>
+          <t>3,88; 27,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 24,87</t>
+          <t>-5,46; 16,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 12,0</t>
+          <t>-2,55; 12,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 21,96</t>
+          <t>8,48; 22,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 22,35</t>
+          <t>4,89; 18,15</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 32,06</t>
+          <t>-5,96; 33,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 49,89</t>
+          <t>7,85; 50,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 46,8</t>
+          <t>10,58; 49,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 27,41</t>
+          <t>-22,27; 22,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,96; 56,03</t>
+          <t>5,62; 53,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 47,6</t>
+          <t>-7,96; 33,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 24,46</t>
+          <t>-4,9; 25,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,77; 44,77</t>
+          <t>15,01; 47,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,4; 45,2</t>
+          <t>9,26; 37,82</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22,1</t>
+          <t>20,61</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,51</t>
+          <t>15,24</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,43</t>
+          <t>18,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 28,76</t>
+          <t>-7,91; 29,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 35,23</t>
+          <t>0,76; 34,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,48; 38,45</t>
+          <t>4,09; 37,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,09; 13,38</t>
+          <t>-23,81; 14,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 37,71</t>
+          <t>1,76; 36,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 29,39</t>
+          <t>-3,1; 28,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 17,1</t>
+          <t>-8,83; 18,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 32,09</t>
+          <t>7,88; 33,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,35; 29,7</t>
+          <t>7,57; 29,34</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>54,62%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 125,17</t>
+          <t>-21,63; 131,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,46; 154,42</t>
+          <t>1,15; 146,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,05; 168,48</t>
+          <t>9,47; 166,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-59,99; 48,05</t>
+          <t>-56,73; 50,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,91; 141,38</t>
+          <t>4,86; 141,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 114,85</t>
+          <t>-7,1; 107,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 60,15</t>
+          <t>-25,46; 65,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,77; 123,15</t>
+          <t>18,05; 124,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,13; 114,29</t>
+          <t>19,26; 107,97</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9,12</t>
+          <t>10,9</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,57</t>
+          <t>9,3</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,3</t>
+          <t>10,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 9,96</t>
+          <t>-5,0; 9,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 14,6</t>
+          <t>0,31; 14,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 16,9</t>
+          <t>4,21; 18,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 8,83</t>
+          <t>-9,82; 9,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,34; 24,1</t>
+          <t>5,95; 24,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,84; 25,42</t>
+          <t>1,01; 17,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 6,98</t>
+          <t>-4,98; 6,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,93; 16,23</t>
+          <t>4,1; 16,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,47; 17,97</t>
+          <t>4,55; 14,96</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 19,98</t>
+          <t>-9,18; 19,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 29,85</t>
+          <t>0,52; 30,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,08; 34,57</t>
+          <t>7,86; 37,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 18,63</t>
+          <t>-17,65; 19,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,71; 51,4</t>
+          <t>10,39; 52,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,2; 53,72</t>
+          <t>1,8; 39,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 14,21</t>
+          <t>-9,2; 13,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,89; 32,86</t>
+          <t>7,53; 32,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,95; 35,9</t>
+          <t>8,39; 30,44</t>
         </is>
       </c>
     </row>
